--- a/data/EGB.MI.xlsx
+++ b/data/EGB.MI.xlsx
@@ -18381,6 +18381,52 @@
         <v>7</v>
       </c>
     </row>
+    <row r="784">
+      <c r="A784" s="1" t="n">
+        <v>46279.2916666667</v>
+      </c>
+      <c r="B784" t="n">
+        <v>0</v>
+      </c>
+      <c r="C784" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="D784" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="E784" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F784" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="G784" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="785">
+      <c r="A785" s="1" t="n">
+        <v>46280.2916666667</v>
+      </c>
+      <c r="B785" t="n">
+        <v>21000</v>
+      </c>
+      <c r="C785" t="n">
+        <v>0.509999990463257</v>
+      </c>
+      <c r="D785" t="n">
+        <v>0.490000009536743</v>
+      </c>
+      <c r="E785" t="n">
+        <v>0.492000013589859</v>
+      </c>
+      <c r="F785" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="G785" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/EGB.MI.xlsx
+++ b/data/EGB.MI.xlsx
@@ -18427,6 +18427,52 @@
         <v>7</v>
       </c>
     </row>
+    <row r="786">
+      <c r="A786" s="1" t="n">
+        <v>46281.2916666667</v>
+      </c>
+      <c r="B786" t="n">
+        <v>0</v>
+      </c>
+      <c r="C786" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="D786" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="E786" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F786" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="G786" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="787">
+      <c r="A787" s="1" t="n">
+        <v>46282.2916666667</v>
+      </c>
+      <c r="B787" t="n">
+        <v>21000</v>
+      </c>
+      <c r="C787" t="n">
+        <v>0.490000009536743</v>
+      </c>
+      <c r="D787" t="n">
+        <v>0.490000009536743</v>
+      </c>
+      <c r="E787" t="n">
+        <v>0.490000009536743</v>
+      </c>
+      <c r="F787" t="n">
+        <v>0.490000009536743</v>
+      </c>
+      <c r="G787" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/EGB.MI.xlsx
+++ b/data/EGB.MI.xlsx
@@ -18291,19 +18291,19 @@
     </row>
     <row r="780">
       <c r="A780" s="1" t="n">
-        <v>46273.2916666667</v>
+        <v>46272.2916666667</v>
       </c>
       <c r="B780" t="n">
-        <v>1000</v>
+        <v>5000</v>
       </c>
       <c r="C780" t="n">
-        <v>0.5</v>
+        <v>0.504999995231628</v>
       </c>
       <c r="D780" t="n">
         <v>0.5</v>
       </c>
       <c r="E780" t="n">
-        <v>0.5</v>
+        <v>0.504999995231628</v>
       </c>
       <c r="F780" t="n">
         <v>0.5</v>
@@ -18314,10 +18314,10 @@
     </row>
     <row r="781">
       <c r="A781" s="1" t="n">
-        <v>46274.2916666667</v>
+        <v>46273.2916666667</v>
       </c>
       <c r="B781" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="C781" t="n">
         <v>0.5</v>
@@ -18337,7 +18337,7 @@
     </row>
     <row r="782">
       <c r="A782" s="1" t="n">
-        <v>46275.2916666667</v>
+        <v>46274.2916666667</v>
       </c>
       <c r="B782" t="n">
         <v>0</v>
@@ -18360,10 +18360,10 @@
     </row>
     <row r="783">
       <c r="A783" s="1" t="n">
-        <v>46276.2916666667</v>
+        <v>46275.2916666667</v>
       </c>
       <c r="B783" t="n">
-        <v>2000</v>
+        <v>0</v>
       </c>
       <c r="C783" t="n">
         <v>0.5</v>
@@ -18383,10 +18383,10 @@
     </row>
     <row r="784">
       <c r="A784" s="1" t="n">
-        <v>46279.2916666667</v>
+        <v>46276.2916666667</v>
       </c>
       <c r="B784" t="n">
-        <v>0</v>
+        <v>2000</v>
       </c>
       <c r="C784" t="n">
         <v>0.5</v>
@@ -18406,19 +18406,19 @@
     </row>
     <row r="785">
       <c r="A785" s="1" t="n">
-        <v>46280.2916666667</v>
+        <v>46279.2916666667</v>
       </c>
       <c r="B785" t="n">
-        <v>21000</v>
+        <v>0</v>
       </c>
       <c r="C785" t="n">
-        <v>0.509999990463257</v>
+        <v>0.5</v>
       </c>
       <c r="D785" t="n">
-        <v>0.490000009536743</v>
+        <v>0.5</v>
       </c>
       <c r="E785" t="n">
-        <v>0.492000013589859</v>
+        <v>0.5</v>
       </c>
       <c r="F785" t="n">
         <v>0.5</v>
@@ -18429,19 +18429,19 @@
     </row>
     <row r="786">
       <c r="A786" s="1" t="n">
-        <v>46281.2916666667</v>
+        <v>46280.2916666667</v>
       </c>
       <c r="B786" t="n">
-        <v>0</v>
+        <v>21000</v>
       </c>
       <c r="C786" t="n">
-        <v>0.5</v>
+        <v>0.509999990463257</v>
       </c>
       <c r="D786" t="n">
-        <v>0.5</v>
+        <v>0.490000009536743</v>
       </c>
       <c r="E786" t="n">
-        <v>0.5</v>
+        <v>0.492000013589859</v>
       </c>
       <c r="F786" t="n">
         <v>0.5</v>
@@ -18452,24 +18452,47 @@
     </row>
     <row r="787">
       <c r="A787" s="1" t="n">
-        <v>46282.2916666667</v>
+        <v>46281.2916666667</v>
       </c>
       <c r="B787" t="n">
-        <v>21000</v>
+        <v>0</v>
       </c>
       <c r="C787" t="n">
-        <v>0.490000009536743</v>
+        <v>0.5</v>
       </c>
       <c r="D787" t="n">
-        <v>0.490000009536743</v>
+        <v>0.5</v>
       </c>
       <c r="E787" t="n">
-        <v>0.490000009536743</v>
+        <v>0.5</v>
       </c>
       <c r="F787" t="n">
-        <v>0.490000009536743</v>
+        <v>0.5</v>
       </c>
       <c r="G787" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="788">
+      <c r="A788" s="1" t="n">
+        <v>46283.2916666667</v>
+      </c>
+      <c r="B788" t="n">
+        <v>7000</v>
+      </c>
+      <c r="C788" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="D788" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="E788" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F788" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="G788" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/EGB.MI.xlsx
+++ b/data/EGB.MI.xlsx
@@ -18475,24 +18475,47 @@
     </row>
     <row r="788">
       <c r="A788" s="1" t="n">
+        <v>46282.2916666667</v>
+      </c>
+      <c r="B788" t="n">
+        <v>21000</v>
+      </c>
+      <c r="C788" t="n">
+        <v>0.490000009536743</v>
+      </c>
+      <c r="D788" t="n">
+        <v>0.490000009536743</v>
+      </c>
+      <c r="E788" t="n">
+        <v>0.490000009536743</v>
+      </c>
+      <c r="F788" t="n">
+        <v>0.490000009536743</v>
+      </c>
+      <c r="G788" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="789">
+      <c r="A789" s="1" t="n">
         <v>46283.2916666667</v>
       </c>
-      <c r="B788" t="n">
+      <c r="B789" t="n">
         <v>7000</v>
       </c>
-      <c r="C788" t="n">
+      <c r="C789" t="n">
         <v>0.5</v>
       </c>
-      <c r="D788" t="n">
+      <c r="D789" t="n">
         <v>0.5</v>
       </c>
-      <c r="E788" t="n">
+      <c r="E789" t="n">
         <v>0.5</v>
       </c>
-      <c r="F788" t="n">
+      <c r="F789" t="n">
         <v>0.5</v>
       </c>
-      <c r="G788" t="s">
+      <c r="G789" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/EGB.MI.xlsx
+++ b/data/EGB.MI.xlsx
@@ -20941,6 +20941,32 @@
         <v>8</v>
       </c>
     </row>
+    <row r="792">
+      <c r="A792" s="1" t="n">
+        <v>46288.2916666667</v>
+      </c>
+      <c r="B792" t="n">
+        <v>3000</v>
+      </c>
+      <c r="C792" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="D792" t="n">
+        <v>0.479999989271164</v>
+      </c>
+      <c r="E792" t="n">
+        <v>0.490000009536743</v>
+      </c>
+      <c r="F792" t="n">
+        <v>0.490000009536743</v>
+      </c>
+      <c r="G792" t="n">
+        <v>0.490000009536743</v>
+      </c>
+      <c r="H792" t="s">
+        <v>8</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/EGB.MI.xlsx
+++ b/data/EGB.MI.xlsx
@@ -20949,10 +20949,10 @@
         <v>3000</v>
       </c>
       <c r="C792" t="n">
-        <v>0.5</v>
+        <v>0.490000009536743</v>
       </c>
       <c r="D792" t="n">
-        <v>0.479999989271164</v>
+        <v>0.490000009536743</v>
       </c>
       <c r="E792" t="n">
         <v>0.490000009536743</v>
@@ -20964,6 +20964,32 @@
         <v>0.490000009536743</v>
       </c>
       <c r="H792" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="793">
+      <c r="A793" s="1" t="n">
+        <v>46289.2916666667</v>
+      </c>
+      <c r="B793" t="n">
+        <v>27000</v>
+      </c>
+      <c r="C793" t="n">
+        <v>0.479999989271164</v>
+      </c>
+      <c r="D793" t="n">
+        <v>0.469999998807907</v>
+      </c>
+      <c r="E793" t="n">
+        <v>0.479999989271164</v>
+      </c>
+      <c r="F793" t="n">
+        <v>0.479999989271164</v>
+      </c>
+      <c r="G793" t="n">
+        <v>0.479999989271164</v>
+      </c>
+      <c r="H793" t="s">
         <v>8</v>
       </c>
     </row>

--- a/data/EGB.MI.xlsx
+++ b/data/EGB.MI.xlsx
@@ -20993,6 +20993,32 @@
         <v>8</v>
       </c>
     </row>
+    <row r="794">
+      <c r="A794" s="1" t="n">
+        <v>46290.2916666667</v>
+      </c>
+      <c r="B794" t="n">
+        <v>27000</v>
+      </c>
+      <c r="C794" t="n">
+        <v>0.469999998807907</v>
+      </c>
+      <c r="D794" t="n">
+        <v>0.451999992132187</v>
+      </c>
+      <c r="E794" t="n">
+        <v>0.469999998807907</v>
+      </c>
+      <c r="F794" t="n">
+        <v>0.469999998807907</v>
+      </c>
+      <c r="G794" t="n">
+        <v>0.469999998807907</v>
+      </c>
+      <c r="H794" t="s">
+        <v>8</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/EGB.MI.xlsx
+++ b/data/EGB.MI.xlsx
@@ -18650,7 +18650,9 @@
       <c r="E795" t="n">
         <v>0.469999998807907</v>
       </c>
-      <c r="F795"/>
+      <c r="F795" t="n">
+        <v>0.469999998807907</v>
+      </c>
       <c r="G795" t="s">
         <v>7</v>
       </c>

--- a/data/EGB.MI.xlsx
+++ b/data/EGB.MI.xlsx
@@ -18657,6 +18657,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="796">
+      <c r="A796" s="1" t="n">
+        <v>46294.2916666667</v>
+      </c>
+      <c r="B796" t="n">
+        <v>0</v>
+      </c>
+      <c r="C796" t="n">
+        <v>0.469999998807907</v>
+      </c>
+      <c r="D796" t="n">
+        <v>0.469999998807907</v>
+      </c>
+      <c r="E796" t="n">
+        <v>0.469999998807907</v>
+      </c>
+      <c r="F796" t="n">
+        <v>0.469999998807907</v>
+      </c>
+      <c r="G796" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/EGB.MI.xlsx
+++ b/data/EGB.MI.xlsx
@@ -18680,6 +18680,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="797">
+      <c r="A797" s="1" t="n">
+        <v>46295.2916666667</v>
+      </c>
+      <c r="B797" t="n">
+        <v>0</v>
+      </c>
+      <c r="C797" t="n">
+        <v>0.469999998807907</v>
+      </c>
+      <c r="D797" t="n">
+        <v>0.469999998807907</v>
+      </c>
+      <c r="E797" t="n">
+        <v>0.469999998807907</v>
+      </c>
+      <c r="F797" t="n">
+        <v>0.469999998807907</v>
+      </c>
+      <c r="G797" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/EGB.MI.xlsx
+++ b/data/EGB.MI.xlsx
@@ -18765,7 +18765,9 @@
       <c r="E800" t="n">
         <v>0.439999997615814</v>
       </c>
-      <c r="F800"/>
+      <c r="F800" t="n">
+        <v>0.437999993562698</v>
+      </c>
       <c r="G800" t="s">
         <v>7</v>
       </c>

--- a/data/EGB.MI.xlsx
+++ b/data/EGB.MI.xlsx
@@ -18772,6 +18772,50 @@
         <v>7</v>
       </c>
     </row>
+    <row r="801">
+      <c r="A801" s="1" t="n">
+        <v>46301.2916666667</v>
+      </c>
+      <c r="B801" t="n">
+        <v>0</v>
+      </c>
+      <c r="C801" t="n">
+        <v>0.437999993562698</v>
+      </c>
+      <c r="D801" t="n">
+        <v>0.437999993562698</v>
+      </c>
+      <c r="E801" t="n">
+        <v>0.437999993562698</v>
+      </c>
+      <c r="F801" t="n">
+        <v>0.437999993562698</v>
+      </c>
+      <c r="G801" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="802">
+      <c r="A802" s="1" t="n">
+        <v>46302.2916666667</v>
+      </c>
+      <c r="B802" t="n">
+        <v>14000</v>
+      </c>
+      <c r="C802" t="n">
+        <v>0.444000005722046</v>
+      </c>
+      <c r="D802" t="n">
+        <v>0.432000011205673</v>
+      </c>
+      <c r="E802" t="n">
+        <v>0.444000005722046</v>
+      </c>
+      <c r="F802"/>
+      <c r="G802" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/EGB.MI.xlsx
+++ b/data/EGB.MI.xlsx
@@ -18811,7 +18811,9 @@
       <c r="E802" t="n">
         <v>0.444000005722046</v>
       </c>
-      <c r="F802"/>
+      <c r="F802" t="n">
+        <v>0.435999989509583</v>
+      </c>
       <c r="G802" t="s">
         <v>7</v>
       </c>

--- a/data/EGB.MI.xlsx
+++ b/data/EGB.MI.xlsx
@@ -18818,6 +18818,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="803">
+      <c r="A803" s="1" t="n">
+        <v>46303.2916666667</v>
+      </c>
+      <c r="B803" t="n">
+        <v>0</v>
+      </c>
+      <c r="C803" t="n">
+        <v>0.435999989509583</v>
+      </c>
+      <c r="D803" t="n">
+        <v>0.435999989509583</v>
+      </c>
+      <c r="E803" t="n">
+        <v>0.435999989509583</v>
+      </c>
+      <c r="F803" t="n">
+        <v>0.435999989509583</v>
+      </c>
+      <c r="G803" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/EGB.MI.xlsx
+++ b/data/EGB.MI.xlsx
@@ -18864,6 +18864,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="805">
+      <c r="A805" s="1" t="n">
+        <v>46307.2916666667</v>
+      </c>
+      <c r="B805" t="n">
+        <v>13000</v>
+      </c>
+      <c r="C805" t="n">
+        <v>0.439999997615814</v>
+      </c>
+      <c r="D805" t="n">
+        <v>0.425999999046326</v>
+      </c>
+      <c r="E805" t="n">
+        <v>0.439999997615814</v>
+      </c>
+      <c r="F805" t="n">
+        <v>0.425999999046326</v>
+      </c>
+      <c r="G805" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/EGB.MI.xlsx
+++ b/data/EGB.MI.xlsx
@@ -18887,6 +18887,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="806">
+      <c r="A806" s="1" t="n">
+        <v>46308.2916666667</v>
+      </c>
+      <c r="B806" t="n">
+        <v>0</v>
+      </c>
+      <c r="C806" t="n">
+        <v>0.425999999046326</v>
+      </c>
+      <c r="D806" t="n">
+        <v>0.425999999046326</v>
+      </c>
+      <c r="E806" t="n">
+        <v>0.425999999046326</v>
+      </c>
+      <c r="F806" t="n">
+        <v>0.425999999046326</v>
+      </c>
+      <c r="G806" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/EGB.MI.xlsx
+++ b/data/EGB.MI.xlsx
@@ -18910,6 +18910,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="807">
+      <c r="A807" s="1" t="n">
+        <v>46309.2916666667</v>
+      </c>
+      <c r="B807" t="n">
+        <v>0</v>
+      </c>
+      <c r="C807" t="n">
+        <v>0.425999999046326</v>
+      </c>
+      <c r="D807" t="n">
+        <v>0.425999999046326</v>
+      </c>
+      <c r="E807" t="n">
+        <v>0.425999999046326</v>
+      </c>
+      <c r="F807" t="n">
+        <v>0.425999999046326</v>
+      </c>
+      <c r="G807" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/EGB.MI.xlsx
+++ b/data/EGB.MI.xlsx
@@ -23868,6 +23868,35 @@
         <v>9</v>
       </c>
     </row>
+    <row r="811">
+      <c r="A811" t="s">
+        <v>9</v>
+      </c>
+      <c r="B811" s="1" t="n">
+        <v>46315.2916666667</v>
+      </c>
+      <c r="C811" t="n">
+        <v>0.407999992370605</v>
+      </c>
+      <c r="D811" t="n">
+        <v>0.407999992370605</v>
+      </c>
+      <c r="E811" t="n">
+        <v>0.407999992370605</v>
+      </c>
+      <c r="F811" t="n">
+        <v>0.40599998831749</v>
+      </c>
+      <c r="G811" t="n">
+        <v>0.40599998831749</v>
+      </c>
+      <c r="H811" t="n">
+        <v>8000</v>
+      </c>
+      <c r="I811" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/EGB.MI.xlsx
+++ b/data/EGB.MI.xlsx
@@ -23882,7 +23882,7 @@
         <v>0.407999992370605</v>
       </c>
       <c r="E811" t="n">
-        <v>0.407999992370605</v>
+        <v>0.40599998831749</v>
       </c>
       <c r="F811" t="n">
         <v>0.40599998831749</v>
@@ -23894,6 +23894,35 @@
         <v>8000</v>
       </c>
       <c r="I811" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="812">
+      <c r="A812" t="s">
+        <v>9</v>
+      </c>
+      <c r="B812" s="1" t="n">
+        <v>46316.2916666667</v>
+      </c>
+      <c r="C812" t="n">
+        <v>0.395999997854233</v>
+      </c>
+      <c r="D812" t="n">
+        <v>0.400000005960464</v>
+      </c>
+      <c r="E812" t="n">
+        <v>0.395999997854233</v>
+      </c>
+      <c r="F812" t="n">
+        <v>0.400000005960464</v>
+      </c>
+      <c r="G812" t="n">
+        <v>0.400000005960464</v>
+      </c>
+      <c r="H812" t="n">
+        <v>5000</v>
+      </c>
+      <c r="I812" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/EGB.MI.xlsx
+++ b/data/EGB.MI.xlsx
@@ -23926,6 +23926,35 @@
         <v>9</v>
       </c>
     </row>
+    <row r="813">
+      <c r="A813" t="s">
+        <v>9</v>
+      </c>
+      <c r="B813" s="1" t="n">
+        <v>46317.2916666667</v>
+      </c>
+      <c r="C813" t="n">
+        <v>0.388000011444092</v>
+      </c>
+      <c r="D813" t="n">
+        <v>0.388000011444092</v>
+      </c>
+      <c r="E813" t="n">
+        <v>0.388000011444092</v>
+      </c>
+      <c r="F813" t="n">
+        <v>0.388000011444092</v>
+      </c>
+      <c r="G813" t="n">
+        <v>0.388000011444092</v>
+      </c>
+      <c r="H813" t="n">
+        <v>7000</v>
+      </c>
+      <c r="I813" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/EGB.MI.xlsx
+++ b/data/EGB.MI.xlsx
@@ -23955,6 +23955,35 @@
         <v>9</v>
       </c>
     </row>
+    <row r="814">
+      <c r="A814" t="s">
+        <v>9</v>
+      </c>
+      <c r="B814" s="1" t="n">
+        <v>46318.2916666667</v>
+      </c>
+      <c r="C814" t="n">
+        <v>0.388000011444092</v>
+      </c>
+      <c r="D814" t="n">
+        <v>0.388000011444092</v>
+      </c>
+      <c r="E814" t="n">
+        <v>0.388000011444092</v>
+      </c>
+      <c r="F814" t="n">
+        <v>0.388000011444092</v>
+      </c>
+      <c r="G814" t="n">
+        <v>0.388000011444092</v>
+      </c>
+      <c r="H814" t="n">
+        <v>1000</v>
+      </c>
+      <c r="I814" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/EGB.MI.xlsx
+++ b/data/EGB.MI.xlsx
@@ -23984,6 +23984,35 @@
         <v>9</v>
       </c>
     </row>
+    <row r="815">
+      <c r="A815" t="s">
+        <v>9</v>
+      </c>
+      <c r="B815" s="1" t="n">
+        <v>46321.3333333333</v>
+      </c>
+      <c r="C815" t="n">
+        <v>0.379999995231628</v>
+      </c>
+      <c r="D815" t="n">
+        <v>0.379999995231628</v>
+      </c>
+      <c r="E815" t="n">
+        <v>0.379999995231628</v>
+      </c>
+      <c r="F815" t="n">
+        <v>0.379999995231628</v>
+      </c>
+      <c r="G815" t="n">
+        <v>0.379999995231628</v>
+      </c>
+      <c r="H815" t="n">
+        <v>3000</v>
+      </c>
+      <c r="I815" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/EGB.MI.xlsx
+++ b/data/EGB.MI.xlsx
@@ -24013,6 +24013,35 @@
         <v>9</v>
       </c>
     </row>
+    <row r="816">
+      <c r="A816" t="s">
+        <v>9</v>
+      </c>
+      <c r="B816" s="1" t="n">
+        <v>46322.3333333333</v>
+      </c>
+      <c r="C816" t="n">
+        <v>0.379999995231628</v>
+      </c>
+      <c r="D816" t="n">
+        <v>0.38400000333786</v>
+      </c>
+      <c r="E816" t="n">
+        <v>0.368000000715256</v>
+      </c>
+      <c r="F816" t="n">
+        <v>0.368000000715256</v>
+      </c>
+      <c r="G816" t="n">
+        <v>0.368000000715256</v>
+      </c>
+      <c r="H816" t="n">
+        <v>17000</v>
+      </c>
+      <c r="I816" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/EGB.MI.xlsx
+++ b/data/EGB.MI.xlsx
@@ -24042,6 +24042,35 @@
         <v>9</v>
       </c>
     </row>
+    <row r="817">
+      <c r="A817" t="s">
+        <v>9</v>
+      </c>
+      <c r="B817" s="1" t="n">
+        <v>46323.3333333333</v>
+      </c>
+      <c r="C817" t="n">
+        <v>0.358000010251999</v>
+      </c>
+      <c r="D817" t="n">
+        <v>0.36599999666214</v>
+      </c>
+      <c r="E817" t="n">
+        <v>0.358000010251999</v>
+      </c>
+      <c r="F817" t="n">
+        <v>0.360000014305115</v>
+      </c>
+      <c r="G817" t="n">
+        <v>0.360000014305115</v>
+      </c>
+      <c r="H817" t="n">
+        <v>16000</v>
+      </c>
+      <c r="I817" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/EGB.MI.xlsx
+++ b/data/EGB.MI.xlsx
@@ -24071,6 +24071,35 @@
         <v>9</v>
       </c>
     </row>
+    <row r="818">
+      <c r="A818" t="s">
+        <v>9</v>
+      </c>
+      <c r="B818" s="1" t="n">
+        <v>46324.3333333333</v>
+      </c>
+      <c r="C818" t="n">
+        <v>0.363999992609024</v>
+      </c>
+      <c r="D818" t="n">
+        <v>0.363999992609024</v>
+      </c>
+      <c r="E818" t="n">
+        <v>0.354000002145767</v>
+      </c>
+      <c r="F818" t="n">
+        <v>0.354000002145767</v>
+      </c>
+      <c r="G818" t="n">
+        <v>0.354000002145767</v>
+      </c>
+      <c r="H818" t="n">
+        <v>28000</v>
+      </c>
+      <c r="I818" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/EGB.MI.xlsx
+++ b/data/EGB.MI.xlsx
@@ -24100,6 +24100,35 @@
         <v>9</v>
       </c>
     </row>
+    <row r="819">
+      <c r="A819" t="s">
+        <v>9</v>
+      </c>
+      <c r="B819" s="1" t="n">
+        <v>46325.3333333333</v>
+      </c>
+      <c r="C819" t="n">
+        <v>0.34400001168251</v>
+      </c>
+      <c r="D819" t="n">
+        <v>0.34400001168251</v>
+      </c>
+      <c r="E819" t="n">
+        <v>0.335999995470047</v>
+      </c>
+      <c r="F819" t="n">
+        <v>0.342000007629395</v>
+      </c>
+      <c r="G819" t="n">
+        <v>0.342000007629395</v>
+      </c>
+      <c r="H819" t="n">
+        <v>13000</v>
+      </c>
+      <c r="I819" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
